--- a/business_forms/035_supplier_credit_assessment_request_form--business_forms.xlsx
+++ b/business_forms/035_supplier_credit_assessment_request_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +617,13 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Contact Person</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +640,13 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,20 +663,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Contact Email</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,13 +686,105 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Supplier Type</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>supplier_credit_assessment_request_form_business_forms_8</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Credit Limit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>supplier_credit_assessment_request_form_business_forms_9</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Payment Terms</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>supplier_credit_assessment_request_form_business_forms_10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Bank Account</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>supplier_credit_assessment_request_form_business_forms_11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Bank Routing Number</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -707,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>business_forms</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Business Forms</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -757,12 +849,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>credit_application_forms</t>
+          <t>international</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Credit Application Forms</t>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>supplier_credit_assessment_request_form_business_forms_2_choices</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>supplier_credit_assessment_request_form_business_forms_7_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>supplier_credit_assessment_request_form_business_forms_7_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>international</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>supplier_credit_assessment_request_form_business_forms_7_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Both</t>
         </is>
       </c>
     </row>
